--- a/design/proposals/CoP_Starter_Card_Stage_Data_PROPOSED.xlsx
+++ b/design/proposals/CoP_Starter_Card_Stage_Data_PROPOSED.xlsx
@@ -9513,486 +9513,486 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>V01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="42" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>Neighbourhood Association Chair</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>町内会長</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="42" t="inlineStr">
         <is>
           <t>Chōnaikai-chō</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="42" t="inlineStr">
         <is>
           <t>Constituents</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="42" t="inlineStr">
         <is>
           <t>The local association wants you at their summer festival. It is the same afternoon as a fundraising lunch.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="42" t="inlineStr">
         <is>
           <t>Attend the festival</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="42" t="n">
         <v>-2</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" s="42" t="inlineStr"/>
+      <c r="N2" s="42" t="inlineStr"/>
+      <c r="O2" s="42" t="inlineStr">
         <is>
           <t>Go to the lunch</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="42" t="n">
         <v>-2</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
+      <c r="S2" s="42" t="inlineStr"/>
+      <c r="T2" s="42" t="inlineStr"/>
+      <c r="U2" s="42" t="inlineStr">
         <is>
           <t>PLACEHOLDER. Trades local goodwill against money.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>V02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>Small Business Owner</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>商店主</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="42" t="inlineStr">
         <is>
           <t>Shōtenshu</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="42" t="inlineStr">
         <is>
           <t>Donors</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="42" t="inlineStr">
         <is>
           <t>A shopkeeper asks you to raise a licensing delay with the ministry. It would cost you a favour.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="42" t="inlineStr">
         <is>
           <t>Make the call</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="42" t="n">
         <v>-2</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="42" t="inlineStr">
         <is>
           <t>Y07</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="42" t="n">
         <v>-3</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="42" t="inlineStr">
         <is>
           <t>Explain you cannot</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="42" t="n">
         <v>-2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
+      <c r="S3" s="42" t="inlineStr"/>
+      <c r="T3" s="42" t="inlineStr"/>
+      <c r="U3" s="42" t="inlineStr">
         <is>
           <t>PLACEHOLDER. Spends party standing for local credit.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>V03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Ministry Official</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>官僚</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>Kanryō</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>Bureaucrats</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>An official offers an early look at a draft report, off the record.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>Accept the briefing</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="42" t="n">
         <v>-3</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" s="42" t="inlineStr"/>
+      <c r="N4" s="42" t="inlineStr"/>
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>Decline politely</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R4" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr"/>
+      <c r="T4" s="42" t="inlineStr"/>
+      <c r="U4" s="42" t="inlineStr">
         <is>
           <t>PLACEHOLDER. Information against propriety. Could later unlock a card.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>V04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>Beat Reporter</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>番記者</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>Bankisha</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
         <is>
           <t>Press</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
         <is>
           <t>A reporter who covers you daily asks for a comment on the bill before the committee sits.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="42" t="inlineStr">
         <is>
           <t>Give a frank comment</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="42" t="n">
         <v>-2</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="42" t="inlineStr">
         <is>
           <t>Y03</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="42" t="inlineStr">
         <is>
           <t>Stay on message</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
+      <c r="S5" s="42" t="inlineStr"/>
+      <c r="T5" s="42" t="inlineStr"/>
+      <c r="U5" s="42" t="inlineStr">
         <is>
           <t>PLACEHOLDER. Candour moves opinion but irritates the party.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>V05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Party Whip's Aide</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>党幹事長室の秘書</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="42" t="inlineStr">
         <is>
           <t>Tō Kanjichō-shitsu no Hisho</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="42" t="inlineStr">
         <is>
           <t>Loyalists</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="42" t="inlineStr">
         <is>
           <t>The whip's office asks you to speak second in the floor debate, backing the party line.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="42" t="inlineStr">
         <is>
           <t>Agree to speak</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" s="42" t="inlineStr"/>
+      <c r="N6" s="42" t="inlineStr"/>
+      <c r="O6" s="42" t="inlineStr">
         <is>
           <t>Ask to be excused</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6" s="42" t="n">
         <v>-4</v>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
+      <c r="S6" s="42" t="inlineStr"/>
+      <c r="T6" s="42" t="inlineStr"/>
+      <c r="U6" s="42" t="inlineStr">
         <is>
           <t>PLACEHOLDER. The clearest party-support lever in office hours.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>V06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Fisheries Co-op Delegate</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>漁協の代表</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="42" t="inlineStr">
         <is>
           <t>Gyokyō no Daihyō</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="42" t="inlineStr">
         <is>
           <t>Constituents</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="42" t="inlineStr">
         <is>
           <t>A co-op delegation wants the coastal provisions strengthened. It would slow the bill.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="42" t="inlineStr">
         <is>
           <t>Back the amendment</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="42" t="n">
         <v>-3</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="42" t="inlineStr">
         <is>
           <t>Y03</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="42" t="inlineStr">
         <is>
           <t>Keep the bill moving</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="42" t="n">
         <v>-3</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" s="42" t="inlineStr">
         <is>
           <t>Y03</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="42" t="n">
         <v>-2</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" s="42" t="inlineStr">
         <is>
           <t>PLACEHOLDER. Uses Environmentalism (Y03) until a Fisheries topic exists — README open decision #12.</t>
         </is>
@@ -15686,7 +15686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="42" min="1" max="1"/>
@@ -15769,6 +15769,16 @@
           <t>Source booster</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Effect key</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Effect key note [PROPOSED]</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" s="43">
       <c r="A2" s="59" t="inlineStr">
@@ -15830,6 +15840,16 @@
           <t>BO03</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>player_start_support</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Start the battle Magnitude ahead.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" s="43">
       <c r="A3" s="59" t="inlineStr">
@@ -15891,6 +15911,16 @@
           <t>BO05</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>kaban_per_stage_win</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Magnitude funds for every stage won.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="43">
       <c r="A4" s="59" t="inlineStr">
@@ -15952,6 +15982,16 @@
           <t>BO08</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>starting_gaffe</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Magnitude off the opening gaffe meter. Wired, but nothing raises the meter yet, so it bites only once something does.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="43">
       <c r="A5" s="59" t="inlineStr">
@@ -16013,6 +16053,16 @@
           <t>BO08</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>player_start_support</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Same key as M01; the magnitude differs.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="26.25" customHeight="1" s="43">
       <c r="A6" s="59" t="inlineStr">
@@ -16074,6 +16124,16 @@
           <t>BO10</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>opp_start_support_on_tag</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Needs bills to carry tags. Named, not built.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26.25" customHeight="1" s="43">
       <c r="A7" s="59" t="inlineStr">
@@ -16135,6 +16195,16 @@
           <t>BO09</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>player_start_support</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Same key again. The audience gate in trigger_segment is what makes it a caucus/floor card.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="32.25" customHeight="1" s="43">
       <c r="A8" s="59" t="inlineStr">
@@ -16426,6 +16496,16 @@
           <t>BO01</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>negates_cold_shoulder</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Needs the module runner (M4).</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26.85" customHeight="1" s="43">
       <c r="A13" s="59" t="inlineStr">
@@ -16485,6 +16565,16 @@
           <t>BO02</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>party_support_per_module</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Needs the module runner (M4).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26.85" customHeight="1" s="43">
       <c r="A14" s="59" t="inlineStr">
@@ -16546,6 +16636,16 @@
           <t>BO04</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>jiban_per_module_win</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Needs the module runner (M4).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26.85" customHeight="1" s="43">
       <c r="A15" s="59" t="inlineStr">
@@ -16607,6 +16707,16 @@
           <t>BO06</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>halve_jiban_losses</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Needs the module runner (M4).</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26.85" customHeight="1" s="43">
       <c r="A16" s="59" t="inlineStr">
@@ -16666,6 +16776,16 @@
       <c r="M16" s="59" t="inlineStr">
         <is>
           <t>BO07</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>opp_start_support_on_tag</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Same; fisheries topic still to be added.</t>
         </is>
       </c>
     </row>
